--- a/jira_export_2026-09-01.xlsx
+++ b/jira_export_2026-09-01.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>38,847 €</t>
+          <t>39,816 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>14,744 €</t>
+          <t>15,350 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>24,104 €</t>
+          <t>24,466 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -8115,7 +8115,7 @@
         <v>725</v>
       </c>
       <c r="O103" s="17" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P103" s="13" t="n">
         <v>0</v>
@@ -8897,10 +8897,10 @@
         <v>1212</v>
       </c>
       <c r="O114" s="17" t="n">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="115">
@@ -12051,10 +12051,10 @@
         <v>46991.995</v>
       </c>
       <c r="O163" s="19" t="n">
-        <v>38847.212</v>
+        <v>39815.712</v>
       </c>
       <c r="P163" s="19" t="n">
-        <v>142.04</v>
+        <v>145.58</v>
       </c>
     </row>
   </sheetData>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>361327</v>
+        <v>360858</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>132769</v>
+        <v>132301</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>228558</v>
@@ -13092,10 +13092,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>165139</v>
+        <v>164533</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>61416</v>
+        <v>60810</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>103722</v>
@@ -13117,10 +13117,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>196188</v>
+        <v>196326</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>71353</v>
+        <v>71490</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>124835</v>
@@ -13669,7 +13669,7 @@
         </is>
       </c>
       <c r="I14" s="27" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15">
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="I22" s="25" t="n">
-        <v>22198</v>
+        <v>22698</v>
       </c>
     </row>
     <row r="23">
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="I24" s="25" t="n">
-        <v>12162</v>
+        <v>12662</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-01.xlsx
+++ b/jira_export_2026-09-01.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>39,816 €</t>
+          <t>40,393 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>24,466 €</t>
+          <t>25,044 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -5329,7 +5329,7 @@
         <v>1207</v>
       </c>
       <c r="O64" s="17" t="n">
-        <v>0</v>
+        <v>301.75</v>
       </c>
       <c r="P64" s="16" t="n">
         <v>0</v>
@@ -5770,62 +5770,70 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J71" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L71" s="12" t="inlineStr"/>
-      <c r="M71" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32607</t>
+        </is>
+      </c>
+      <c r="M71" s="12" t="inlineStr">
+        <is>
+          <t>00163155</t>
+        </is>
+      </c>
       <c r="N71" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="P71" s="13" t="n">
         <v>0</v>
@@ -5834,12 +5842,12 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
@@ -5849,12 +5857,12 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
@@ -5864,7 +5872,7 @@
       </c>
       <c r="G72" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
@@ -5881,22 +5889,14 @@
         <v>4</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M72" s="15" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L72" s="15" t="inlineStr"/>
+      <c r="M72" s="15" t="inlineStr"/>
       <c r="N72" s="16" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O72" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="16" t="n">
@@ -5906,32 +5906,32 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -5941,32 +5941,32 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O73" s="17" t="n">
         <v>0</v>
@@ -5978,32 +5978,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6013,34 +6013,34 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="16" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O74" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="16" t="n">
@@ -6050,32 +6050,32 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -6085,34 +6085,34 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>450</v>
-      </c>
-      <c r="O75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
@@ -6122,32 +6122,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6157,65 +6157,69 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O76" s="17" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -6225,64 +6229,60 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="13" t="n">
-        <v>127.5</v>
+        <v>910</v>
+      </c>
+      <c r="O77" s="17" t="n">
+        <v>91</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C78" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr"/>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6309,52 +6309,52 @@
         <v>5</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>100</v>
+        <v>127.5</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
@@ -6385,53 +6385,53 @@
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>590.15</v>
+        <v>0</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>793.65</v>
+        <v>100</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>3174.6</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6446,64 +6446,64 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>12.75</v>
+        <v>0.25</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>0</v>
+        <v>590.15</v>
       </c>
       <c r="O80" s="16" t="n">
-        <v>109.972</v>
+        <v>793.65</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>8.630000000000001</v>
+        <v>3174.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6513,69 +6513,69 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>285</v>
-      </c>
-      <c r="O81" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>109.972</v>
       </c>
       <c r="P81" s="13" t="n">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
@@ -6601,16 +6601,16 @@
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O82" s="17" t="n">
         <v>0</v>
@@ -6622,12 +6622,12 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
@@ -6673,16 +6673,16 @@
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O83" s="17" t="n">
         <v>0</v>
@@ -6694,32 +6694,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
@@ -6741,52 +6741,52 @@
         <v>5</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O84" s="17" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -6801,49 +6801,49 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O85" s="17" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="P85" s="13" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
@@ -6889,16 +6889,16 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O86" s="17" t="n">
         <v>0</v>
@@ -6910,32 +6910,32 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
@@ -6945,49 +6945,49 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>700</v>
-      </c>
-      <c r="O87" s="13" t="n">
-        <v>1934.1</v>
+        <v>300</v>
+      </c>
+      <c r="O87" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>126.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="G88" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H88" s="15" t="inlineStr">
@@ -7029,44 +7029,52 @@
         <v>6</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L88" s="15" t="inlineStr"/>
-      <c r="M88" s="15" t="inlineStr"/>
+        <v>15.25</v>
+      </c>
+      <c r="L88" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N88" s="16" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="O88" s="16" t="n">
-        <v>0</v>
+        <v>1934.1</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0</v>
+        <v>126.83</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -7076,7 +7084,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -7086,64 +7094,56 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L89" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M89" s="12" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L89" s="12" t="inlineStr"/>
+      <c r="M89" s="12" t="inlineStr"/>
       <c r="N89" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="13" t="n">
-        <v>138.825</v>
+        <v>0</v>
       </c>
       <c r="P89" s="13" t="n">
-        <v>15.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -7153,49 +7153,49 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>210</v>
-      </c>
-      <c r="O90" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O90" s="16" t="n">
+        <v>138.825</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>0</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
@@ -7241,16 +7241,16 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O91" s="17" t="n">
         <v>0</v>
@@ -7262,12 +7262,12 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
@@ -7313,16 +7313,16 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O92" s="17" t="n">
         <v>0</v>
@@ -7334,12 +7334,12 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -7374,29 +7374,29 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="13" t="n">
+        <v>255</v>
+      </c>
+      <c r="O93" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
@@ -7406,12 +7406,12 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7446,29 +7446,29 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="O94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
@@ -7478,27 +7478,27 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
@@ -7529,19 +7529,19 @@
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="13" t="n">
-        <v>200</v>
+        <v>140</v>
+      </c>
+      <c r="O95" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
         <v>0</v>
@@ -7550,32 +7550,32 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -7585,64 +7585,64 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>690</v>
-      </c>
-      <c r="O96" s="17" t="n">
-        <v>230</v>
+        <v>0</v>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>200</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>26.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -7662,44 +7662,44 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>1</v>
+        <v>8.75</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="13" t="n">
-        <v>0</v>
+        <v>690</v>
+      </c>
+      <c r="O97" s="17" t="n">
+        <v>230</v>
       </c>
       <c r="P97" s="13" t="n">
-        <v>0</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
@@ -7734,23 +7734,23 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
@@ -7766,12 +7766,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -7781,12 +7781,12 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -7806,33 +7806,33 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>2.42</v>
+        <v>0.25</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O99" s="13" t="n">
-        <v>224.05</v>
+        <v>0</v>
       </c>
       <c r="P99" s="13" t="n">
-        <v>92.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -7889,22 +7889,22 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O100" s="17" t="n">
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+      <c r="O100" s="16" t="n">
+        <v>224.05</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>25.86</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7961,47 +7961,49 @@
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O101" s="17" t="n">
-        <v>262.5</v>
+        <v>62.5</v>
       </c>
       <c r="P101" s="13" t="n">
-        <v>108.62</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
@@ -8020,64 +8022,62 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.5</v>
+        <v>2.42</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="16" t="n">
-        <v>0</v>
+        <v>787.5</v>
+      </c>
+      <c r="O102" s="17" t="n">
+        <v>262.5</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>0</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v/>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -8087,35 +8087,35 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>725</v>
-      </c>
-      <c r="O103" s="17" t="n">
-        <v>362.5</v>
+        <v>0</v>
+      </c>
+      <c r="O103" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
         <v>0</v>
@@ -8124,30 +8124,32 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
@@ -8157,49 +8159,49 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="16" t="n">
-        <v>1351.26</v>
+        <v>725</v>
+      </c>
+      <c r="O104" s="17" t="n">
+        <v>362.5</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>450.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -8209,13 +8211,11 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v/>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
@@ -8234,33 +8234,33 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O105" s="13" t="n">
-        <v>0</v>
+        <v>1351.26</v>
       </c>
       <c r="P105" s="13" t="n">
-        <v>0</v>
+        <v>450.42</v>
       </c>
     </row>
     <row r="106">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8533,18 +8533,18 @@
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O109" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
@@ -8554,12 +8554,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8569,11 +8569,13 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
@@ -8587,49 +8589,49 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>4.25</v>
+        <v>1.95</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="16" t="n">
-        <v>98.28</v>
+        <v>1320</v>
+      </c>
+      <c r="O110" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>23.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -8639,7 +8641,7 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E111" s="12" t="n">
@@ -8657,65 +8659,63 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>11.5</v>
+        <v>4.25</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O111" s="13" t="n">
-        <v>1280</v>
+        <v>98.28</v>
       </c>
       <c r="P111" s="13" t="n">
-        <v>111.3</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v/>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
@@ -8734,58 +8734,60 @@
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0.25</v>
+        <v>11.5</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O112" s="16" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25354</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Duncan HAMELIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE PLAN D'ORGON</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8804,23 +8806,23 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26768</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00141775</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
@@ -8836,22 +8838,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>MAIRIE DE PLAN D'ORGON</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8874,60 +8876,58 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O114" s="17" t="n">
-        <v>606</v>
+        <v>0</v>
+      </c>
+      <c r="O114" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v/>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
@@ -8946,59 +8946,59 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="13" t="n">
-        <v>0</v>
+        <v>1212</v>
+      </c>
+      <c r="O115" s="17" t="n">
+        <v>606</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E116" s="15" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
@@ -9008,27 +9008,35 @@
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" s="15" t="inlineStr"/>
-      <c r="M116" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L116" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M116" s="15" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N116" s="16" t="n">
         <v>0</v>
       </c>
@@ -9042,26 +9050,28 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
@@ -9070,35 +9080,27 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L117" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M117" s="12" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L117" s="12" t="inlineStr"/>
+      <c r="M117" s="12" t="inlineStr"/>
       <c r="N117" s="13" t="n">
         <v>0</v>
       </c>
@@ -9161,12 +9163,12 @@
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9182,22 +9184,22 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9220,23 +9222,23 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9252,12 +9254,12 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -9267,7 +9269,7 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9290,23 +9292,23 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.75</v>
+        <v>3.25</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9322,22 +9324,22 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9355,28 +9357,28 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>13</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9392,22 +9394,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9425,28 +9427,28 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9511,12 +9513,12 @@
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9547,7 +9549,7 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9581,12 +9583,12 @@
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9617,7 +9619,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9651,12 +9653,12 @@
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9672,22 +9674,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9705,34 +9707,34 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
-        <v>401</v>
-      </c>
-      <c r="O126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="16" t="n">
@@ -9742,22 +9744,22 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9773,24 +9775,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H127" s="12" t="inlineStr"/>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K127" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="L127" s="12" t="inlineStr"/>
-      <c r="M127" s="12" t="inlineStr"/>
+      <c r="L127" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M127" s="12" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N127" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="13" t="n">
+        <v>401</v>
+      </c>
+      <c r="O127" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9800,22 +9814,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9831,11 +9845,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H128" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H128" s="15" t="inlineStr"/>
       <c r="I128" s="15" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -9845,18 +9855,10 @@
         <v>16</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M128" s="15" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr"/>
+      <c r="M128" s="15" t="inlineStr"/>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
@@ -9870,22 +9872,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9903,28 +9905,28 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0.5</v>
+        <v>8.25</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
@@ -9940,22 +9942,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9978,29 +9980,29 @@
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="16" t="n">
@@ -10010,22 +10012,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10038,27 +10040,39 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H131" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L131" s="12" t="inlineStr"/>
-      <c r="M131" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N131" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="13" t="n">
+        <v>230</v>
+      </c>
+      <c r="O131" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
@@ -10068,22 +10082,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10096,35 +10110,23 @@
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H132" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="inlineStr"/>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M132" s="15" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr"/>
+      <c r="M132" s="15" t="inlineStr"/>
       <c r="N132" s="16" t="n">
         <v>0</v>
       </c>
@@ -10138,12 +10140,12 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -10153,7 +10155,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10171,28 +10173,28 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10208,22 +10210,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10241,28 +10243,28 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10327,12 +10329,12 @@
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10348,12 +10350,12 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
@@ -10363,7 +10365,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10376,27 +10378,35 @@
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" s="15" t="inlineStr"/>
-      <c r="M136" s="15" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M136" s="15" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
@@ -10410,22 +10420,22 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10443,7 +10453,7 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
@@ -10455,7 +10465,7 @@
         <v>20</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>11.25</v>
+        <v>1</v>
       </c>
       <c r="L137" s="12" t="inlineStr"/>
       <c r="M137" s="12" t="inlineStr"/>
@@ -10472,12 +10482,12 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
@@ -10487,7 +10497,7 @@
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10510,14 +10520,14 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>1.5</v>
+        <v>11.25</v>
       </c>
       <c r="L138" s="15" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -10534,22 +10544,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10557,44 +10567,36 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M139" s="12" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L139" s="12" t="inlineStr"/>
+      <c r="M139" s="12" t="inlineStr"/>
       <c r="N139" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O139" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P139" s="13" t="n">
@@ -10604,22 +10606,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10627,7 +10629,7 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
@@ -10637,34 +10639,34 @@
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O140" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="16" t="n">
@@ -10689,7 +10691,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10723,7 +10725,7 @@
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
@@ -10744,12 +10746,12 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
@@ -10759,7 +10761,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10789,22 +10791,22 @@
         <v>20</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O142" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="16" t="n">
@@ -10814,22 +10816,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10842,7 +10844,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -10852,21 +10854,29 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L143" s="12" t="inlineStr"/>
-      <c r="M143" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N143" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" s="13" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O143" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="13" t="n">
@@ -10876,12 +10886,12 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
@@ -10891,7 +10901,7 @@
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10914,14 +10924,14 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L144" s="15" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -10938,22 +10948,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -10976,25 +10986,17 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
         <v>28</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M145" s="12" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr"/>
+      <c r="M145" s="12" t="inlineStr"/>
       <c r="N145" s="13" t="n">
         <v>0</v>
       </c>
@@ -11008,22 +11010,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11046,17 +11048,25 @@
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr"/>
-      <c r="M146" s="15" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M146" s="15" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11070,22 +11080,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11108,14 +11118,14 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L147" s="12" t="inlineStr"/>
       <c r="M147" s="12" t="inlineStr"/>
@@ -11132,12 +11142,12 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -11147,7 +11157,7 @@
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11165,19 +11175,19 @@
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
         <v>33</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -11194,22 +11204,22 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11232,14 +11242,14 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L149" s="12" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr"/>
@@ -11256,22 +11266,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11284,35 +11294,27 @@
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L150" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M150" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L150" s="15" t="inlineStr"/>
+      <c r="M150" s="15" t="inlineStr"/>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
@@ -11326,22 +11328,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11354,23 +11356,35 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H151" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr"/>
-      <c r="M151" s="12" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M151" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
@@ -11384,12 +11398,12 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
@@ -11399,7 +11413,7 @@
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11415,14 +11429,10 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H152" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H152" s="15" t="inlineStr"/>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
@@ -11431,16 +11441,8 @@
       <c r="K152" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="L152" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M152" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+      <c r="L152" s="15" t="inlineStr"/>
+      <c r="M152" s="15" t="inlineStr"/>
       <c r="N152" s="16" t="n">
         <v>0</v>
       </c>
@@ -11454,12 +11456,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -11469,7 +11471,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11492,17 +11494,25 @@
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L153" s="12" t="inlineStr"/>
-      <c r="M153" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L153" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M153" s="12" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N153" s="13" t="n">
         <v>0</v>
       </c>
@@ -11516,28 +11526,26 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E154" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v/>
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
@@ -11551,7 +11559,7 @@
       </c>
       <c r="H154" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I154" s="15" t="inlineStr">
@@ -11563,7 +11571,7 @@
         <v>35</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L154" s="15" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -11580,23 +11588,27 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C155" s="12" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
@@ -11611,19 +11623,19 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>11</v>
+        <v>1.25</v>
       </c>
       <c r="L155" s="12" t="inlineStr"/>
       <c r="M155" s="12" t="inlineStr"/>
@@ -11640,27 +11652,23 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C156" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="inlineStr"/>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E156" s="15" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F156" s="15" t="inlineStr">
@@ -11675,19 +11683,19 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -11704,21 +11712,29 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C157" s="12" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E157" s="12" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11726,17 +11742,21 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H157" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K157" s="12" t="n">
         <v>0.5</v>
@@ -11756,18 +11776,18 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr"/>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E158" s="15" t="inlineStr"/>
@@ -11784,14 +11804,14 @@
       <c r="H158" s="15" t="inlineStr"/>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L158" s="15" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -11808,18 +11828,18 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr"/>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr"/>
@@ -11830,36 +11850,28 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr"/>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M159" s="12" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L159" s="12" t="inlineStr"/>
+      <c r="M159" s="12" t="inlineStr"/>
       <c r="N159" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O159" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P159" s="13" t="n">
         <v>0</v>
@@ -11868,18 +11880,18 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr"/>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E160" s="15" t="inlineStr"/>
@@ -11896,50 +11908,50 @@
       <c r="H160" s="15" t="inlineStr"/>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M160" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N160" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O160" s="16" t="n">
-        <v>595.7</v>
+        <v>100</v>
       </c>
       <c r="P160" s="16" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr"/>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr"/>
@@ -11950,48 +11962,56 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr"/>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L161" s="12" t="inlineStr"/>
-      <c r="M161" s="12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L161" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M161" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N161" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O161" s="13" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
       <c r="P161" s="13" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr"/>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E162" s="15" t="inlineStr"/>
@@ -12008,11 +12028,11 @@
       <c r="H162" s="15" t="inlineStr"/>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K162" s="15" t="n">
         <v>0.25</v>
@@ -12030,31 +12050,83 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="18" t="inlineStr">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr"/>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr"/>
+      <c r="F163" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G163" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H163" s="12" t="inlineStr"/>
+      <c r="I163" s="12" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J163" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K163" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L163" s="12" t="inlineStr"/>
+      <c r="M163" s="12" t="inlineStr"/>
+      <c r="N163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B163" s="18" t="inlineStr"/>
-      <c r="C163" s="18" t="inlineStr"/>
-      <c r="D163" s="18" t="inlineStr"/>
-      <c r="E163" s="18" t="inlineStr"/>
-      <c r="F163" s="18" t="inlineStr"/>
-      <c r="G163" s="18" t="inlineStr"/>
-      <c r="H163" s="18" t="inlineStr"/>
-      <c r="I163" s="18" t="inlineStr"/>
-      <c r="J163" s="18" t="inlineStr"/>
-      <c r="K163" s="18" t="inlineStr"/>
-      <c r="L163" s="18" t="inlineStr"/>
-      <c r="M163" s="18" t="inlineStr"/>
-      <c r="N163" s="19" t="n">
+      <c r="B164" s="18" t="inlineStr"/>
+      <c r="C164" s="18" t="inlineStr"/>
+      <c r="D164" s="18" t="inlineStr"/>
+      <c r="E164" s="18" t="inlineStr"/>
+      <c r="F164" s="18" t="inlineStr"/>
+      <c r="G164" s="18" t="inlineStr"/>
+      <c r="H164" s="18" t="inlineStr"/>
+      <c r="I164" s="18" t="inlineStr"/>
+      <c r="J164" s="18" t="inlineStr"/>
+      <c r="K164" s="18" t="inlineStr"/>
+      <c r="L164" s="18" t="inlineStr"/>
+      <c r="M164" s="18" t="inlineStr"/>
+      <c r="N164" s="19" t="n">
         <v>46991.995</v>
       </c>
-      <c r="O163" s="19" t="n">
-        <v>39815.712</v>
-      </c>
-      <c r="P163" s="19" t="n">
-        <v>145.58</v>
+      <c r="O164" s="19" t="n">
+        <v>40393.462</v>
+      </c>
+      <c r="P164" s="19" t="n">
+        <v>147.69</v>
       </c>
     </row>
   </sheetData>
@@ -12218,6 +12290,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13067,16 +13140,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>360858</v>
+        <v>362786</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>132301</v>
+        <v>134530</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>228558</v>
+        <v>228256</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>145176</v>
+        <v>144874</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21179</v>
@@ -13117,16 +13190,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>196326</v>
+        <v>198253</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>71490</v>
+        <v>73719</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>124835</v>
+        <v>124534</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>58546</v>
+        <v>58244</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>9871</v>
@@ -13624,7 +13697,7 @@
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>0</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="14">
@@ -14005,7 +14078,7 @@
         </is>
       </c>
       <c r="I22" s="25" t="n">
-        <v>22698</v>
+        <v>25202</v>
       </c>
     </row>
     <row r="23">
@@ -14047,7 +14120,7 @@
         </is>
       </c>
       <c r="I24" s="25" t="n">
-        <v>12662</v>
+        <v>15166</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-01.xlsx
+++ b/jira_export_2026-09-01.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>40,393 €</t>
+          <t>40,643 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>15,350 €</t>
+          <t>15,600 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P164"/>
+  <dimension ref="A1:P166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -7694,27 +7694,27 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
@@ -7741,23 +7741,23 @@
         <v>7</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="P98" s="16" t="n">
         <v>0</v>
@@ -7766,12 +7766,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -7781,12 +7781,12 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -7806,23 +7806,23 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
@@ -7838,12 +7838,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -7878,33 +7878,33 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>2.42</v>
+        <v>0.25</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="16" t="n">
-        <v>224.05</v>
+        <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>92.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -7961,22 +7961,22 @@
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O101" s="17" t="n">
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>224.05</v>
       </c>
       <c r="P101" s="13" t="n">
-        <v>25.86</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -8033,47 +8033,49 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O102" s="17" t="n">
-        <v>262.5</v>
+        <v>62.5</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>108.62</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
@@ -8092,64 +8094,62 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0.5</v>
+        <v>2.42</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="13" t="n">
-        <v>0</v>
+        <v>787.5</v>
+      </c>
+      <c r="O103" s="17" t="n">
+        <v>262.5</v>
       </c>
       <c r="P103" s="13" t="n">
-        <v>0</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v/>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
@@ -8159,35 +8159,35 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>725</v>
-      </c>
-      <c r="O104" s="17" t="n">
-        <v>362.5</v>
+        <v>0</v>
+      </c>
+      <c r="O104" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
         <v>0</v>
@@ -8196,30 +8196,32 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -8229,49 +8231,49 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="13" t="n">
-        <v>1351.26</v>
+        <v>725</v>
+      </c>
+      <c r="O105" s="17" t="n">
+        <v>362.5</v>
       </c>
       <c r="P105" s="13" t="n">
-        <v>450.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8281,13 +8283,11 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v/>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
@@ -8306,33 +8306,33 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O106" s="16" t="n">
-        <v>0</v>
+        <v>1351.26</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>0</v>
+        <v>450.42</v>
       </c>
     </row>
     <row r="107">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
@@ -8605,18 +8605,18 @@
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8626,12 +8626,12 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -8641,11 +8641,13 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
@@ -8659,49 +8661,49 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>4.25</v>
+        <v>1.95</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="13" t="n">
-        <v>98.28</v>
+        <v>1320</v>
+      </c>
+      <c r="O111" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
-        <v>23.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -8711,7 +8713,7 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E112" s="15" t="n">
@@ -8729,65 +8731,63 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>11.5</v>
+        <v>4.25</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O112" s="16" t="n">
-        <v>1280</v>
+        <v>98.28</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>111.3</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v/>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8806,58 +8806,60 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0.25</v>
+        <v>11.5</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O113" s="13" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="P113" s="13" t="n">
-        <v>0</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-25354</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Duncan HAMELIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE PLAN D'ORGON</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
@@ -8876,23 +8878,23 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26768</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00141775</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
@@ -8908,22 +8910,22 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>MAIRIE DE PLAN D'ORGON</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8946,60 +8948,58 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O115" s="17" t="n">
-        <v>606</v>
+        <v>0</v>
+      </c>
+      <c r="O115" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v/>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
@@ -9018,59 +9018,59 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="16" t="n">
-        <v>0</v>
+        <v>1212</v>
+      </c>
+      <c r="O116" s="17" t="n">
+        <v>606</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
@@ -9080,27 +9080,35 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="12" t="inlineStr"/>
-      <c r="M117" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L117" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M117" s="12" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N117" s="13" t="n">
         <v>0</v>
       </c>
@@ -9114,26 +9122,28 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -9142,35 +9152,27 @@
       </c>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L118" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M118" s="15" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L118" s="15" t="inlineStr"/>
+      <c r="M118" s="15" t="inlineStr"/>
       <c r="N118" s="16" t="n">
         <v>0</v>
       </c>
@@ -9233,12 +9235,12 @@
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9254,22 +9256,22 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9292,23 +9294,23 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9324,12 +9326,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9339,7 +9341,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9362,23 +9364,23 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.75</v>
+        <v>3.25</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9394,22 +9396,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9427,28 +9429,28 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9464,22 +9466,22 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9497,28 +9499,28 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
         <v>13</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9583,12 +9585,12 @@
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9619,7 +9621,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9653,12 +9655,12 @@
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9689,7 +9691,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9723,12 +9725,12 @@
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9744,22 +9746,22 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9777,34 +9779,34 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
-        <v>401</v>
-      </c>
-      <c r="O127" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9814,22 +9816,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9845,24 +9847,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H128" s="15" t="inlineStr"/>
+      <c r="H128" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K128" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="L128" s="15" t="inlineStr"/>
-      <c r="M128" s="15" t="inlineStr"/>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M128" s="15" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N128" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="O128" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9872,22 +9886,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9903,11 +9917,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H129" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H129" s="12" t="inlineStr"/>
       <c r="I129" s="12" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -9917,18 +9927,10 @@
         <v>16</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="L129" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M129" s="12" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr"/>
+      <c r="M129" s="12" t="inlineStr"/>
       <c r="N129" s="13" t="n">
         <v>0</v>
       </c>
@@ -9942,22 +9944,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9975,28 +9977,28 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.5</v>
+        <v>8.25</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
@@ -10012,22 +10014,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10050,29 +10052,29 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
-        <v>230</v>
-      </c>
-      <c r="O131" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
@@ -10082,22 +10084,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10110,27 +10112,39 @@
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H132" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr"/>
-      <c r="M132" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M132" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O132" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="16" t="n">
@@ -10140,22 +10154,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10168,35 +10182,23 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H133" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="inlineStr"/>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L133" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M133" s="12" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L133" s="12" t="inlineStr"/>
+      <c r="M133" s="12" t="inlineStr"/>
       <c r="N133" s="13" t="n">
         <v>0</v>
       </c>
@@ -10210,12 +10212,12 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
@@ -10225,7 +10227,7 @@
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10243,28 +10245,28 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10280,22 +10282,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10313,28 +10315,28 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10399,12 +10401,12 @@
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
@@ -10420,12 +10422,12 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10435,7 +10437,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10448,27 +10450,35 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L137" s="12" t="inlineStr"/>
-      <c r="M137" s="12" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N137" s="13" t="n">
         <v>0</v>
       </c>
@@ -10482,22 +10492,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10515,7 +10525,7 @@
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
@@ -10527,7 +10537,7 @@
         <v>20</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>11.25</v>
+        <v>1</v>
       </c>
       <c r="L138" s="15" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -10544,12 +10554,12 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
@@ -10559,7 +10569,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10582,14 +10592,14 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>1.5</v>
+        <v>11.25</v>
       </c>
       <c r="L139" s="12" t="inlineStr"/>
       <c r="M139" s="12" t="inlineStr"/>
@@ -10606,22 +10616,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10629,44 +10639,36 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M140" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L140" s="15" t="inlineStr"/>
+      <c r="M140" s="15" t="inlineStr"/>
       <c r="N140" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="16" t="n">
@@ -10676,22 +10678,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10699,7 +10701,7 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -10709,34 +10711,34 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O141" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P141" s="13" t="n">
@@ -10761,7 +10763,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10795,7 +10797,7 @@
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
@@ -10816,12 +10818,12 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
@@ -10831,7 +10833,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10861,22 +10863,22 @@
         <v>20</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="13" t="n">
@@ -10886,22 +10888,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10914,7 +10916,7 @@
       </c>
       <c r="G144" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H144" s="15" t="inlineStr">
@@ -10924,21 +10926,29 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L144" s="15" t="inlineStr"/>
-      <c r="M144" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L144" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M144" s="15" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N144" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O144" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P144" s="16" t="n">
@@ -10948,12 +10958,12 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
@@ -10963,7 +10973,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -10986,14 +10996,14 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L145" s="12" t="inlineStr"/>
       <c r="M145" s="12" t="inlineStr"/>
@@ -11010,22 +11020,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11048,25 +11058,17 @@
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>28</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M146" s="15" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr"/>
+      <c r="M146" s="15" t="inlineStr"/>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11080,22 +11082,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11118,17 +11120,25 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L147" s="12" t="inlineStr"/>
-      <c r="M147" s="12" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L147" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M147" s="12" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N147" s="13" t="n">
         <v>0</v>
       </c>
@@ -11142,22 +11152,22 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11180,14 +11190,14 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -11204,12 +11214,12 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -11219,7 +11229,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11237,19 +11247,19 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
         <v>33</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L149" s="12" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr"/>
@@ -11266,22 +11276,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11304,14 +11314,14 @@
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L150" s="15" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -11328,22 +11338,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11356,35 +11366,27 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr"/>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
@@ -11398,22 +11400,22 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11426,23 +11428,35 @@
       </c>
       <c r="G152" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H152" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L152" s="15" t="inlineStr"/>
-      <c r="M152" s="15" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L152" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M152" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N152" s="16" t="n">
         <v>0</v>
       </c>
@@ -11456,12 +11470,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -11471,7 +11485,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11487,14 +11501,10 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H153" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H153" s="12" t="inlineStr"/>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
@@ -11503,16 +11513,8 @@
       <c r="K153" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L153" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M153" s="12" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+      <c r="L153" s="12" t="inlineStr"/>
+      <c r="M153" s="12" t="inlineStr"/>
       <c r="N153" s="13" t="n">
         <v>0</v>
       </c>
@@ -11526,12 +11528,12 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
@@ -11541,7 +11543,7 @@
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11564,17 +11566,25 @@
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L154" s="15" t="inlineStr"/>
-      <c r="M154" s="15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L154" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M154" s="15" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N154" s="16" t="n">
         <v>0</v>
       </c>
@@ -11588,28 +11598,26 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="n">
+        <v/>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
@@ -11623,7 +11631,7 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
@@ -11635,7 +11643,7 @@
         <v>35</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L155" s="12" t="inlineStr"/>
       <c r="M155" s="12" t="inlineStr"/>
@@ -11652,23 +11660,27 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C156" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E156" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F156" s="15" t="inlineStr">
@@ -11683,19 +11695,19 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>11</v>
+        <v>1.25</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -11712,27 +11724,23 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C157" s="12" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr"/>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
@@ -11747,19 +11755,19 @@
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="L157" s="12" t="inlineStr"/>
       <c r="M157" s="12" t="inlineStr"/>
@@ -11776,21 +11784,29 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C158" s="15" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C158" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E158" s="15" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E158" s="15" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11798,17 +11814,21 @@
       </c>
       <c r="G158" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H158" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H158" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K158" s="15" t="n">
         <v>0.5</v>
@@ -11828,18 +11848,18 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr"/>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr"/>
@@ -11856,14 +11876,14 @@
       <c r="H159" s="12" t="inlineStr"/>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L159" s="12" t="inlineStr"/>
       <c r="M159" s="12" t="inlineStr"/>
@@ -11880,18 +11900,18 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr"/>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E160" s="15" t="inlineStr"/>
@@ -11902,36 +11922,28 @@
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H160" s="15" t="inlineStr"/>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M160" s="15" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L160" s="15" t="inlineStr"/>
+      <c r="M160" s="15" t="inlineStr"/>
       <c r="N160" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O160" s="16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P160" s="16" t="n">
         <v>0</v>
@@ -11940,18 +11952,18 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr"/>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr"/>
@@ -11968,50 +11980,50 @@
       <c r="H161" s="12" t="inlineStr"/>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N161" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O161" s="13" t="n">
-        <v>595.7</v>
+        <v>100</v>
       </c>
       <c r="P161" s="13" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr"/>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E162" s="15" t="inlineStr"/>
@@ -12022,28 +12034,36 @@
       </c>
       <c r="G162" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H162" s="15" t="inlineStr"/>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L162" s="15" t="inlineStr"/>
-      <c r="M162" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L162" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M162" s="15" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N162" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O162" s="16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P162" s="16" t="n">
         <v>0</v>
@@ -12052,18 +12072,18 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr"/>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr"/>
@@ -12074,59 +12094,171 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr"/>
       <c r="I163" s="12" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J163" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M163" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="13" t="n">
+        <v>595.7</v>
+      </c>
+      <c r="P163" s="13" t="n">
+        <v>595.7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="14" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B164" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C164" s="15" t="inlineStr"/>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E164" s="15" t="inlineStr"/>
+      <c r="F164" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G164" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H164" s="15" t="inlineStr"/>
+      <c r="I164" s="15" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="J164" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K164" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L164" s="15" t="inlineStr"/>
+      <c r="M164" s="15" t="inlineStr"/>
+      <c r="N164" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr"/>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="inlineStr"/>
+      <c r="F165" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G165" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H165" s="12" t="inlineStr"/>
+      <c r="I165" s="12" t="inlineStr">
+        <is>
           <t>20/03/2025</t>
         </is>
       </c>
-      <c r="J163" s="12" t="n">
+      <c r="J165" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K163" s="12" t="n">
+      <c r="K165" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="L163" s="12" t="inlineStr"/>
-      <c r="M163" s="12" t="inlineStr"/>
-      <c r="N163" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="18" t="inlineStr">
+      <c r="L165" s="12" t="inlineStr"/>
+      <c r="M165" s="12" t="inlineStr"/>
+      <c r="N165" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B164" s="18" t="inlineStr"/>
-      <c r="C164" s="18" t="inlineStr"/>
-      <c r="D164" s="18" t="inlineStr"/>
-      <c r="E164" s="18" t="inlineStr"/>
-      <c r="F164" s="18" t="inlineStr"/>
-      <c r="G164" s="18" t="inlineStr"/>
-      <c r="H164" s="18" t="inlineStr"/>
-      <c r="I164" s="18" t="inlineStr"/>
-      <c r="J164" s="18" t="inlineStr"/>
-      <c r="K164" s="18" t="inlineStr"/>
-      <c r="L164" s="18" t="inlineStr"/>
-      <c r="M164" s="18" t="inlineStr"/>
-      <c r="N164" s="19" t="n">
+      <c r="B166" s="18" t="inlineStr"/>
+      <c r="C166" s="18" t="inlineStr"/>
+      <c r="D166" s="18" t="inlineStr"/>
+      <c r="E166" s="18" t="inlineStr"/>
+      <c r="F166" s="18" t="inlineStr"/>
+      <c r="G166" s="18" t="inlineStr"/>
+      <c r="H166" s="18" t="inlineStr"/>
+      <c r="I166" s="18" t="inlineStr"/>
+      <c r="J166" s="18" t="inlineStr"/>
+      <c r="K166" s="18" t="inlineStr"/>
+      <c r="L166" s="18" t="inlineStr"/>
+      <c r="M166" s="18" t="inlineStr"/>
+      <c r="N166" s="19" t="n">
         <v>46991.995</v>
       </c>
-      <c r="O164" s="19" t="n">
-        <v>40393.462</v>
-      </c>
-      <c r="P164" s="19" t="n">
-        <v>147.69</v>
+      <c r="O166" s="19" t="n">
+        <v>40643.462</v>
+      </c>
+      <c r="P166" s="19" t="n">
+        <v>148.6</v>
       </c>
     </row>
   </sheetData>
@@ -12291,6 +12423,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13140,13 +13274,13 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>362786</v>
+        <v>366386</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>134530</v>
+        <v>138205</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>228256</v>
+        <v>228181</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>144874</v>
@@ -13165,13 +13299,13 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>164533</v>
+        <v>164283</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>60810</v>
+        <v>60635</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>103722</v>
+        <v>103647</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>86630</v>
@@ -13190,10 +13324,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>198253</v>
+        <v>202103</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>73719</v>
+        <v>77569</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>124534</v>
@@ -13337,7 +13471,7 @@
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>0</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="6">
@@ -13787,7 +13921,7 @@
         </is>
       </c>
       <c r="I15" s="26" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="16">
@@ -14078,7 +14212,7 @@
         </is>
       </c>
       <c r="I22" s="25" t="n">
-        <v>25202</v>
+        <v>29052</v>
       </c>
     </row>
     <row r="23">
@@ -14120,7 +14254,7 @@
         </is>
       </c>
       <c r="I24" s="25" t="n">
-        <v>15166</v>
+        <v>19016</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-01.xlsx
+++ b/jira_export_2026-09-01.xlsx
@@ -252,14 +252,14 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>0 h</t>
+          <t>5 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -942,7 +942,7 @@
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1054,27 +1054,27 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -1094,131 +1094,123 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="inlineStr">
+        <v>0.25</v>
+      </c>
+      <c r="L5" s="11" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr"/>
+      <c r="N5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-34975</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE SURESNES</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-34979</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M6" s="14" t="inlineStr">
         <is>
           <t>00178226</t>
         </is>
       </c>
-      <c r="N5" s="12" t="n">
+      <c r="N6" s="15" t="n">
         <v>1100</v>
       </c>
-      <c r="O5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34819</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Ville de Bourges</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>Migration GEODP Placier et ODP</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>29/07/2026</t>
-        </is>
-      </c>
-      <c r="J6" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34825</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
-        <is>
-          <t>00177218</t>
-        </is>
-      </c>
-      <c r="N6" s="16" t="n">
-        <v>2419</v>
-      </c>
-      <c r="O6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="16" t="n">
+      <c r="O6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1238,29 +1230,29 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N7" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O7" s="13" t="n">
+        <v>2419</v>
+      </c>
+      <c r="O7" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="12" t="n">
@@ -1268,106 +1260,106 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34249</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE VIENNE</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-34718</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE VILLEURBANNE</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Crédits d'heure (14h)</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
-      <c r="N8" s="16" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="16" t="n">
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34722</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="inlineStr">
+        <is>
+          <t>00176875</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n">
+        <v>1260</v>
+      </c>
+      <c r="O8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1377,12 +1369,12 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
@@ -1393,18 +1385,18 @@
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>4536</v>
-      </c>
-      <c r="O9" s="13" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="O9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="12" t="n">
@@ -1412,106 +1404,106 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34208</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>Migration GEODP Placier 2</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-34249</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VIENNE</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration Placier et ODP </t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="n">
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34216</t>
-        </is>
-      </c>
-      <c r="M10" s="15" t="inlineStr">
-        <is>
-          <t>00171155</t>
-        </is>
-      </c>
-      <c r="N10" s="16" t="n">
-        <v>525</v>
-      </c>
-      <c r="O10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="16" t="n">
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34258</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="inlineStr">
+        <is>
+          <t>00171361</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="n">
+        <v>2127.2</v>
+      </c>
+      <c r="O10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1521,12 +1513,12 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
@@ -1537,18 +1529,18 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1662</v>
-      </c>
-      <c r="O11" s="13" t="n">
+        <v>4536</v>
+      </c>
+      <c r="O11" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="12" t="n">
@@ -1556,101 +1548,101 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34169</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-34208</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHATEAUGIRON</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier 2</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="n">
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M12" s="15" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
-      <c r="N12" s="16" t="n">
-        <v>9623.1</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="16" t="n">
+      <c r="K12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34216</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
+        <is>
+          <t>00171155</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="n">
+        <v>525</v>
+      </c>
+      <c r="O12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1665,12 +1657,12 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
@@ -1681,18 +1673,18 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>707</v>
-      </c>
-      <c r="O13" s="13" t="n">
+        <v>1662</v>
+      </c>
+      <c r="O13" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="12" t="n">
@@ -1700,101 +1692,101 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34064</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-34169</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>Alizée MARGOT</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>VILLE DE VANNES</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Migration GEODP 1 vers GEODP 2</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="n">
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34070</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
-        <is>
-          <t>00170468</t>
-        </is>
-      </c>
-      <c r="N14" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="O14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="16" t="n">
+      <c r="K14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34227</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>2026-0210095</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="n">
+        <v>9623.1</v>
+      </c>
+      <c r="O14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1814,7 +1806,7 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
@@ -1825,18 +1817,18 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>510</v>
-      </c>
-      <c r="O15" s="13" t="n">
+        <v>707</v>
+      </c>
+      <c r="O15" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -1844,106 +1836,106 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33949</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Commune de Colmar</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-34064</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE VANNES</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="J16" s="15" t="n">
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33955</t>
-        </is>
-      </c>
-      <c r="M16" s="15" t="inlineStr">
-        <is>
-          <t>00170302</t>
-        </is>
-      </c>
-      <c r="N16" s="16" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="16" t="n">
+      <c r="K16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34070</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>00170468</t>
+        </is>
+      </c>
+      <c r="N16" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="O16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1953,12 +1945,12 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
@@ -1969,18 +1961,18 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>220</v>
-      </c>
-      <c r="O17" s="13" t="n">
+        <v>510</v>
+      </c>
+      <c r="O17" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="12" t="n">
@@ -1988,101 +1980,101 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33804</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>Purge arrêtés temporaires</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-33949</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Commune de Colmar</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="J18" s="15" t="n">
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="K18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33808</t>
-        </is>
-      </c>
-      <c r="M18" s="15" t="inlineStr">
-        <is>
-          <t>00169856</t>
-        </is>
-      </c>
-      <c r="N18" s="16" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="16" t="n">
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33955</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
+        <is>
+          <t>00170302</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="O18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2102,7 +2094,7 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
@@ -2113,18 +2105,18 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>920</v>
-      </c>
-      <c r="O19" s="13" t="n">
+        <v>220</v>
+      </c>
+      <c r="O19" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="12" t="n">
@@ -2132,106 +2124,106 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33471</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-33813</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Fabien REUTENAUER</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE D AUCH</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>FDS Facture LiS</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Modélisation Seyne S/ Mer</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33475</t>
-        </is>
-      </c>
-      <c r="M20" s="15" t="inlineStr">
-        <is>
-          <t>00168025</t>
-        </is>
-      </c>
-      <c r="N20" s="16" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="16" t="n">
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33817</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>00169865</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -2246,29 +2238,29 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>344</v>
-      </c>
-      <c r="O21" s="13" t="n">
+        <v>1890</v>
+      </c>
+      <c r="O21" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="12" t="n">
@@ -2276,106 +2268,106 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33266</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>MAIRIE DE CAPBRETON</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-33739</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>UPSELL PASTELL + DA DPA</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33272</t>
-        </is>
-      </c>
-      <c r="M22" s="15" t="inlineStr">
-        <is>
-          <t>00166910</t>
-        </is>
-      </c>
-      <c r="N22" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="O22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="16" t="n">
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33745</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
+          <t>00169509</t>
+        </is>
+      </c>
+      <c r="N22" s="15" t="n">
+        <v>920</v>
+      </c>
+      <c r="O22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2385,12 +2377,12 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
@@ -2401,18 +2393,18 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>149</v>
-      </c>
-      <c r="O23" s="13" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="O23" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
@@ -2420,101 +2412,101 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33227</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>21 crédits d'heure</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-33395</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTBELIARD</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="n">
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33232</t>
-        </is>
-      </c>
-      <c r="M24" s="15" t="inlineStr">
-        <is>
-          <t>00166708</t>
-        </is>
-      </c>
-      <c r="N24" s="16" t="n">
-        <v>625</v>
-      </c>
-      <c r="O24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="16" t="n">
+      <c r="K24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33401</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>00167624</t>
+        </is>
+      </c>
+      <c r="N24" s="15" t="n">
+        <v>344</v>
+      </c>
+      <c r="O24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2529,12 +2521,12 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
@@ -2545,18 +2537,18 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O25" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="O25" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
@@ -2564,86 +2556,86 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33064</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-33239</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Maxime PONTONNIER</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>MAIRIE DE LONGWY</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LODEVE</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Migracier activité Placier vers Geodp V2</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G26" s="15" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H26" s="15" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="J26" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33073</t>
-        </is>
-      </c>
-      <c r="M26" s="15" t="inlineStr">
-        <is>
-          <t>00165708</t>
-        </is>
-      </c>
-      <c r="N26" s="16" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="16" t="n">
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33245</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>00166748</t>
+        </is>
+      </c>
+      <c r="N26" s="15" t="n">
+        <v>149</v>
+      </c>
+      <c r="O26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2653,12 +2645,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2678,29 +2670,29 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K27" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O27" s="13" t="n">
+        <v>625</v>
+      </c>
+      <c r="O27" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="12" t="n">
@@ -2708,101 +2700,101 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-32552</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G28" s="15" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-33170</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Commune de Bonneville</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H28" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M28" s="15" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
-      <c r="N28" s="16" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="16" t="n">
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33177</t>
+        </is>
+      </c>
+      <c r="M28" s="14" t="inlineStr">
+        <is>
+          <t>00166356</t>
+        </is>
+      </c>
+      <c r="N28" s="15" t="n">
+        <v>910</v>
+      </c>
+      <c r="O28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2822,29 +2814,29 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2335</v>
-      </c>
-      <c r="O29" s="13" t="n">
+        <v>1207</v>
+      </c>
+      <c r="O29" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
@@ -2852,101 +2844,101 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-32331</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-32984</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Interface Civil net finance avec Littéralis</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H30" s="15" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-32340</t>
-        </is>
-      </c>
-      <c r="M30" s="15" t="inlineStr">
-        <is>
-          <t>00161493</t>
-        </is>
-      </c>
-      <c r="N30" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="16" t="n">
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32990</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>00165270</t>
+        </is>
+      </c>
+      <c r="N30" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2966,29 +2958,29 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
@@ -2996,101 +2988,101 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-32086</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G32" s="15" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-32552</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE CHALON SUR SAONE</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H32" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>17/03/2026</t>
-        </is>
-      </c>
-      <c r="J32" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-32095</t>
-        </is>
-      </c>
-      <c r="M32" s="15" t="inlineStr">
-        <is>
-          <t>00160474</t>
-        </is>
-      </c>
-      <c r="N32" s="16" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="16" t="n">
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32556</t>
+        </is>
+      </c>
+      <c r="M32" s="14" t="inlineStr">
+        <is>
+          <t>00162313</t>
+        </is>
+      </c>
+      <c r="N32" s="15" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3105,12 +3097,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3121,18 +3113,18 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O33" s="13" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="12" t="n">
@@ -3140,86 +3132,86 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31967</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-32331</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration GEODP Placier </t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H34" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="J34" s="15" t="n">
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="K34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31971</t>
-        </is>
-      </c>
-      <c r="M34" s="15" t="inlineStr">
-        <is>
-          <t>00159863</t>
-        </is>
-      </c>
-      <c r="N34" s="16" t="n">
-        <v>1325</v>
-      </c>
-      <c r="O34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="16" t="n">
+      <c r="K34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32340</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="inlineStr">
+        <is>
+          <t>00161493</t>
+        </is>
+      </c>
+      <c r="N34" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3229,12 +3221,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3254,7 +3246,7 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3265,18 +3257,18 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="O35" s="13" t="n">
+        <v>910</v>
+      </c>
+      <c r="O35" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
@@ -3284,101 +3276,101 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31908</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-32086</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>Maxime PONTONNIER</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>Commune de GUINGAMP</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Acquisition Geodp Placier</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G36" s="15" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H36" s="15" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="J36" s="15" t="n">
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="K36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31917</t>
-        </is>
-      </c>
-      <c r="M36" s="15" t="inlineStr">
-        <is>
-          <t>00159608</t>
-        </is>
-      </c>
-      <c r="N36" s="16" t="n">
-        <v>588</v>
-      </c>
-      <c r="O36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="16" t="n">
+      <c r="K36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-32095</t>
+        </is>
+      </c>
+      <c r="M36" s="14" t="inlineStr">
+        <is>
+          <t>00160474</t>
+        </is>
+      </c>
+      <c r="N36" s="15" t="n">
+        <v>590.15</v>
+      </c>
+      <c r="O36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3393,34 +3385,34 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K37" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O37" s="13" t="n">
+        <v>285</v>
+      </c>
+      <c r="O37" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
@@ -3428,86 +3420,86 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31589</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31967</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU LOT -CD46</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H38" s="15" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>26/02/2026</t>
-        </is>
-      </c>
-      <c r="J38" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="K38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31596</t>
-        </is>
-      </c>
-      <c r="M38" s="15" t="inlineStr">
-        <is>
-          <t>00157967</t>
-        </is>
-      </c>
-      <c r="N38" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="O38" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="16" t="n">
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31971</t>
+        </is>
+      </c>
+      <c r="M38" s="14" t="inlineStr">
+        <is>
+          <t>00159863</t>
+        </is>
+      </c>
+      <c r="N38" s="15" t="n">
+        <v>1325</v>
+      </c>
+      <c r="O38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3517,12 +3509,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3542,29 +3534,29 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>700</v>
-      </c>
-      <c r="O39" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="O39" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -3572,101 +3564,101 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31351</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31908</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>Maxime PONTONNIER</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>Migration vers GeoDP V2</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Commune de GUINGAMP</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G40" s="15" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H40" s="15" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>17/02/2026</t>
-        </is>
-      </c>
-      <c r="J40" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="K40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31360</t>
-        </is>
-      </c>
-      <c r="M40" s="15" t="inlineStr">
-        <is>
-          <t>00157041</t>
-        </is>
-      </c>
-      <c r="N40" s="16" t="n">
-        <v>210</v>
-      </c>
-      <c r="O40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="16" t="n">
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31917</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
+        <is>
+          <t>00159608</t>
+        </is>
+      </c>
+      <c r="N40" s="15" t="n">
+        <v>588</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3681,12 +3673,12 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3697,18 +3689,18 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="O41" s="13" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="O41" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="12" t="n">
@@ -3716,250 +3708,250 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31036</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>Migration V2 classique + abo CB</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31589</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H42" s="15" t="inlineStr">
+      <c r="H42" s="14" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>10/02/2026</t>
-        </is>
-      </c>
-      <c r="J42" s="15" t="n">
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="K42" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31045</t>
-        </is>
-      </c>
-      <c r="M42" s="15" t="inlineStr">
-        <is>
-          <t>00156095</t>
-        </is>
-      </c>
-      <c r="N42" s="16" t="n">
-        <v>255</v>
-      </c>
-      <c r="O42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="16" t="n">
+      <c r="K42" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31596</t>
+        </is>
+      </c>
+      <c r="M42" s="14" t="inlineStr">
+        <is>
+          <t>00157967</t>
+        </is>
+      </c>
+      <c r="N42" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE MONTELIMAR</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation LiEx</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
+      <c r="N43" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="O43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31351</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
           <t>Maxime PONTONNIER</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>COMMUNE DE ALENCON</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>Migration 1 activité GEODP2</t>
-        </is>
-      </c>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="G43" s="11" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H44" s="14" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>28/01/2026</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-30335</t>
-        </is>
-      </c>
-      <c r="M43" s="11" t="inlineStr">
-        <is>
-          <t>00154411</t>
-        </is>
-      </c>
-      <c r="N43" s="12" t="n">
-        <v>140</v>
-      </c>
-      <c r="O43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-30196</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>CD56</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>Paramétrage interface Pastell</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>21/01/2026</t>
-        </is>
-      </c>
-      <c r="J44" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="K44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-30197</t>
-        </is>
-      </c>
-      <c r="M44" s="15" t="inlineStr">
-        <is>
-          <t>00153939</t>
-        </is>
-      </c>
-      <c r="N44" s="16" t="n">
-        <v>690</v>
-      </c>
-      <c r="O44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="16" t="n">
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31360</t>
+        </is>
+      </c>
+      <c r="M44" s="14" t="inlineStr">
+        <is>
+          <t>00157041</t>
+        </is>
+      </c>
+      <c r="N44" s="15" t="n">
+        <v>210</v>
+      </c>
+      <c r="O44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3969,34 +3961,34 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K45" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O45" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="O45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
@@ -4004,86 +3996,86 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-29606</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>COMMUNE DE BIARRITZ</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>Paramétrages complémentaires + Vision</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G46" s="15" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31036</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Maxime PONTONNIER</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2 classique + abo CB</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H46" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>09/01/2026</t>
-        </is>
-      </c>
-      <c r="J46" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="K46" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-29608</t>
-        </is>
-      </c>
-      <c r="M46" s="15" t="inlineStr">
-        <is>
-          <t>00152338</t>
-        </is>
-      </c>
-      <c r="N46" s="16" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="16" t="n">
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K46" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31045</t>
+        </is>
+      </c>
+      <c r="M46" s="14" t="inlineStr">
+        <is>
+          <t>00156095</t>
+        </is>
+      </c>
+      <c r="N46" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="O46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4093,12 +4085,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4118,29 +4110,29 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>725</v>
-      </c>
-      <c r="O47" s="13" t="n">
+        <v>140</v>
+      </c>
+      <c r="O47" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="12" t="n">
@@ -4148,100 +4140,102 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28095</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-30196</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>Remy VINCENT</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>CD56</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>Paramétrage interface Pastell</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H48" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>24/11/2025</t>
-        </is>
-      </c>
-      <c r="J48" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="K48" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28202</t>
-        </is>
-      </c>
-      <c r="M48" s="15" t="inlineStr">
-        <is>
-          <t>00144857</t>
-        </is>
-      </c>
-      <c r="N48" s="16" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="16" t="n">
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>21/01/2026</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K48" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-30197</t>
+        </is>
+      </c>
+      <c r="M48" s="14" t="inlineStr">
+        <is>
+          <t>00153939</t>
+        </is>
+      </c>
+      <c r="N48" s="15" t="n">
+        <v>690</v>
+      </c>
+      <c r="O48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
@@ -4255,34 +4249,34 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K49" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O49" s="13" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="O49" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
@@ -4290,234 +4284,240 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-21661</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>[Grand Dax] - Pastell</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-29606</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>Fabien REUTENAUER</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>GRAND DAX</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v/>
-      </c>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G50" s="15" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="H50" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>07/05/2025</t>
-        </is>
-      </c>
-      <c r="J50" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="K50" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27373</t>
-        </is>
-      </c>
-      <c r="M50" s="15" t="inlineStr">
-        <is>
-          <t>466234</t>
-        </is>
-      </c>
-      <c r="N50" s="16" t="n">
-        <v>401</v>
-      </c>
-      <c r="O50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="16" t="n">
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-29608</t>
+        </is>
+      </c>
+      <c r="M50" s="14" t="inlineStr">
+        <is>
+          <t>00152338</t>
+        </is>
+      </c>
+      <c r="N50" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28310</t>
+        </is>
+      </c>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>00145374</t>
+        </is>
+      </c>
+      <c r="N51" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-28095</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>14/04/2025</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="K51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M51" s="11" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
-      <c r="N51" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-18115</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>BISCHWILLER</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v/>
-      </c>
-      <c r="F52" s="15" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>17/12/2024</t>
-        </is>
-      </c>
-      <c r="J52" s="15" t="n">
-        <v>21</v>
-      </c>
-      <c r="K52" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M52" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
-      <c r="N52" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O52" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="16" t="n">
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K52" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28202</t>
+        </is>
+      </c>
+      <c r="M52" s="14" t="inlineStr">
+        <is>
+          <t>00144857</t>
+        </is>
+      </c>
+      <c r="N52" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -4535,65 +4535,347 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>00141205</t>
+        </is>
+      </c>
+      <c r="N53" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-21661</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>[Grand Dax] - Pastell</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>GRAND DAX</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>07/05/2025</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K54" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M54" s="14" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
+      <c r="N54" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-20907</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>SAINT PIERRE (LA REUNION)</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>14/04/2025</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
+      <c r="N55" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K56" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M56" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N56" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
         <is>
           <t>12/12/2024</t>
         </is>
       </c>
-      <c r="J53" s="11" t="n">
+      <c r="J57" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="K53" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="11" t="inlineStr">
+      <c r="K57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-28023</t>
         </is>
       </c>
-      <c r="M53" s="11" t="inlineStr">
+      <c r="M57" s="11" t="inlineStr">
         <is>
           <t>454387</t>
         </is>
       </c>
-      <c r="N53" s="12" t="n">
+      <c r="N57" s="12" t="n">
         <v>557.145</v>
       </c>
-      <c r="O53" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="O57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B54" s="17" t="inlineStr"/>
-      <c r="C54" s="17" t="inlineStr"/>
-      <c r="D54" s="17" t="inlineStr"/>
-      <c r="E54" s="17" t="inlineStr"/>
-      <c r="F54" s="17" t="inlineStr"/>
-      <c r="G54" s="17" t="inlineStr"/>
-      <c r="H54" s="17" t="inlineStr"/>
-      <c r="I54" s="17" t="inlineStr"/>
-      <c r="J54" s="17" t="inlineStr"/>
-      <c r="K54" s="17" t="inlineStr"/>
-      <c r="L54" s="17" t="inlineStr"/>
-      <c r="M54" s="17" t="inlineStr"/>
-      <c r="N54" s="18" t="n">
-        <v>46991.995</v>
-      </c>
-      <c r="O54" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="18" t="n"/>
+      <c r="B58" s="17" t="inlineStr"/>
+      <c r="C58" s="17" t="inlineStr"/>
+      <c r="D58" s="17" t="inlineStr"/>
+      <c r="E58" s="17" t="inlineStr"/>
+      <c r="F58" s="17" t="inlineStr"/>
+      <c r="G58" s="17" t="inlineStr"/>
+      <c r="H58" s="17" t="inlineStr"/>
+      <c r="I58" s="17" t="inlineStr"/>
+      <c r="J58" s="17" t="inlineStr"/>
+      <c r="K58" s="17" t="inlineStr"/>
+      <c r="L58" s="17" t="inlineStr"/>
+      <c r="M58" s="17" t="inlineStr"/>
+      <c r="N58" s="18" t="n">
+        <v>48251.995</v>
+      </c>
+      <c r="O58" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:P4"/>
@@ -4647,6 +4929,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4806,12 +5092,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Collaborateurs actifs ce mois</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -4830,12 +5116,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Total jours travaillés (équipe)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>184 j</t>
         </is>
@@ -4894,17 +5180,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="14" t="n">
         <v>96.59999999999999</v>
       </c>
     </row>
@@ -4964,17 +5250,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5034,17 +5320,17 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5104,17 +5390,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="C32" s="15" t="n">
+      <c r="C32" s="14" t="n">
         <v>96.59999999999999</v>
       </c>
     </row>
@@ -5215,32 +5501,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Littéralis</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n">
+      <c r="B5" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5537,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -5260,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -5270,7 +5556,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5568,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -5370,13 +5656,13 @@
         <v>366386</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>138205</v>
+        <v>134295</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>228181</v>
+        <v>232090</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>144874</v>
+        <v>148784</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -5386,7 +5672,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Littéralis</t>
         </is>
@@ -5420,13 +5706,13 @@
         <v>202103</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>77569</v>
+        <v>73660</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>124534</v>
+        <v>128443</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>58244</v>
+        <v>62154</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>9871</v>

--- a/jira_export_2026-09-01.xlsx
+++ b/jira_export_2026-09-01.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0 €</t>
+          <t>362 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>0 €</t>
+          <t>362 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>5 h</t>
+          <t>11 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1334,12 +1334,12 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1374,29 +1374,29 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="12" t="n">
@@ -1406,27 +1406,27 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
@@ -1457,16 +1457,16 @@
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>2127.2</v>
+        <v>769.5</v>
       </c>
       <c r="O10" s="16" t="n">
         <v>0</v>
@@ -1478,32 +1478,32 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
@@ -1529,16 +1529,16 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O11" s="16" t="n">
         <v>0</v>
@@ -1550,32 +1550,32 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
@@ -1601,16 +1601,16 @@
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O12" s="16" t="n">
         <v>0</v>
@@ -1622,12 +1622,12 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1673,16 +1673,16 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1694,27 +1694,27 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
@@ -1745,16 +1745,16 @@
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>0</v>
@@ -1766,12 +1766,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
@@ -1817,16 +1817,16 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O15" s="16" t="n">
         <v>0</v>
@@ -1838,12 +1838,12 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
@@ -1889,16 +1889,16 @@
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>0</v>
@@ -1910,27 +1910,27 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
@@ -1961,16 +1961,16 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1982,32 +1982,32 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
@@ -2033,16 +2033,16 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2054,27 +2054,27 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2105,16 +2105,16 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2126,12 +2126,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="O20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="15" t="n">
@@ -2198,12 +2198,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2245,22 +2245,22 @@
         <v>3</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="12" t="n">
@@ -2270,27 +2270,27 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
@@ -2321,16 +2321,16 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2342,27 +2342,27 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2382,27 +2382,27 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>171.4</v>
+        <v>920</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2414,32 +2414,32 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
@@ -2465,16 +2465,16 @@
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2486,27 +2486,27 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
@@ -2537,16 +2537,16 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>0</v>
@@ -2558,27 +2558,27 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2609,16 +2609,16 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2630,32 +2630,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2681,16 +2681,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2702,32 +2702,32 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
@@ -2753,16 +2753,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2774,12 +2774,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2814,27 +2814,27 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2846,32 +2846,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2881,32 +2881,32 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2918,27 +2918,27 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2958,29 +2958,29 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="O31" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
@@ -2990,12 +2990,12 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="15" t="n">
@@ -3062,32 +3062,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3097,32 +3097,32 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3134,27 +3134,27 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3185,16 +3185,16 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3206,32 +3206,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3257,16 +3257,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3278,32 +3278,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
@@ -3329,16 +3329,16 @@
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3350,12 +3350,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3401,16 +3401,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>285</v>
+        <v>590.15</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3422,32 +3422,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
@@ -3473,16 +3473,16 @@
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3494,12 +3494,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3545,16 +3545,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3566,32 +3566,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
@@ -3617,16 +3617,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3638,27 +3638,27 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3673,32 +3673,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3710,12 +3710,12 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
@@ -3761,16 +3761,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3782,32 +3782,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3833,16 +3833,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3854,32 +3854,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
@@ -3905,16 +3905,16 @@
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3926,12 +3926,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3977,16 +3977,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3998,12 +3998,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
@@ -4049,16 +4049,16 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4070,12 +4070,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4110,27 +4110,27 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4142,32 +4142,32 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4193,16 +4193,16 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4214,27 +4214,27 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4265,16 +4265,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4337,16 +4337,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4358,32 +4358,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4393,32 +4393,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K51" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4430,32 +4430,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4481,19 +4481,19 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O52" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O52" s="15" t="n">
+        <v>362.5</v>
       </c>
       <c r="P52" s="15" t="n">
         <v>0</v>
@@ -4502,12 +4502,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4517,11 +4517,13 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
@@ -4540,27 +4542,27 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K53" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>1212</v>
+        <v>1320</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4572,22 +4574,22 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E54" s="14" t="n">
@@ -4605,32 +4607,32 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K54" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>401</v>
+        <v>1212</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4642,12 +4644,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4657,7 +4659,7 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -4680,27 +4682,27 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>230</v>
+        <v>401</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4712,22 +4714,22 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E56" s="14" t="n">
@@ -4735,7 +4737,7 @@
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4745,32 +4747,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K56" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4782,22 +4784,22 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -4805,7 +4807,7 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4815,12 +4817,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4831,50 +4833,120 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M57" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N57" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K58" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-28023</t>
         </is>
       </c>
-      <c r="M57" s="11" t="inlineStr">
+      <c r="M58" s="14" t="inlineStr">
         <is>
           <t>454387</t>
         </is>
       </c>
-      <c r="N57" s="12" t="n">
+      <c r="N58" s="15" t="n">
         <v>557.145</v>
       </c>
-      <c r="O57" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="O58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B58" s="17" t="inlineStr"/>
-      <c r="C58" s="17" t="inlineStr"/>
-      <c r="D58" s="17" t="inlineStr"/>
-      <c r="E58" s="17" t="inlineStr"/>
-      <c r="F58" s="17" t="inlineStr"/>
-      <c r="G58" s="17" t="inlineStr"/>
-      <c r="H58" s="17" t="inlineStr"/>
-      <c r="I58" s="17" t="inlineStr"/>
-      <c r="J58" s="17" t="inlineStr"/>
-      <c r="K58" s="17" t="inlineStr"/>
-      <c r="L58" s="17" t="inlineStr"/>
-      <c r="M58" s="17" t="inlineStr"/>
-      <c r="N58" s="18" t="n">
-        <v>48251.995</v>
-      </c>
-      <c r="O58" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="18" t="n">
-        <v>0</v>
+      <c r="B59" s="17" t="inlineStr"/>
+      <c r="C59" s="17" t="inlineStr"/>
+      <c r="D59" s="17" t="inlineStr"/>
+      <c r="E59" s="17" t="inlineStr"/>
+      <c r="F59" s="17" t="inlineStr"/>
+      <c r="G59" s="17" t="inlineStr"/>
+      <c r="H59" s="17" t="inlineStr"/>
+      <c r="I59" s="17" t="inlineStr"/>
+      <c r="J59" s="17" t="inlineStr"/>
+      <c r="K59" s="17" t="inlineStr"/>
+      <c r="L59" s="17" t="inlineStr"/>
+      <c r="M59" s="17" t="inlineStr"/>
+      <c r="N59" s="18" t="n">
+        <v>47526.995</v>
+      </c>
+      <c r="O59" s="18" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="P59" s="18" t="n">
+        <v>76.31999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4933,6 +5005,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5537,7 +5610,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -5546,17 +5619,17 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>275.31</v>
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5641,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -5653,16 +5726,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>366386</v>
+        <v>366023</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>134295</v>
+        <v>137842</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>232090</v>
+        <v>228181</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>148784</v>
+        <v>144874</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -5703,16 +5776,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>202103</v>
+        <v>201740</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>73660</v>
+        <v>77207</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>128443</v>
+        <v>124534</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>62154</v>
+        <v>58244</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>9871</v>
@@ -5732,17 +5805,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -5756,7 +5829,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 0 commande(s)</t>
+          <t>Épics créées ce mois — 1 commande(s)</t>
         </is>
       </c>
     </row>
@@ -5806,6 +5879,114 @@
         <is>
           <t>Montant (€)</t>
         </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35392</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35385</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE ROUEN</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>00179700</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="17" t="n"/>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>1 commande(s)</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>0 commande(s)</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>1 commande(s)</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-01.xlsx
+++ b/jira_export_2026-09-01.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>11 h</t>
+          <t>27 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1054,27 +1054,27 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>[COMMUNE DE GAILLARD] - Prestation forfait - Reprise de charte graphique</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marine MASINGARBE</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>Prestation forfait - Reprise de charte graphique</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -1094,17 +1094,25 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="J5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L5" s="11" t="inlineStr"/>
-      <c r="M5" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35188</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>00178947</t>
+        </is>
+      </c>
       <c r="N5" s="12" t="n">
         <v>0</v>
       </c>
@@ -1118,27 +1126,27 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1148,7 +1156,7 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -1158,29 +1166,21 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J6" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34979</t>
-        </is>
-      </c>
-      <c r="M6" s="14" t="inlineStr">
-        <is>
-          <t>00178226</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L6" s="14" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
       <c r="N6" s="15" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="15" t="n">
@@ -1190,32 +1190,32 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -1225,32 +1225,32 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N7" s="12" t="n">
-        <v>2419</v>
+        <v>1100</v>
       </c>
       <c r="O7" s="16" t="n">
         <v>0</v>
@@ -1262,32 +1262,32 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
@@ -1313,16 +1313,16 @@
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N8" s="15" t="n">
-        <v>1260</v>
+        <v>2419</v>
       </c>
       <c r="O8" s="16" t="n">
         <v>0</v>
@@ -1334,32 +1334,32 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1369,34 +1369,34 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="O9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="12" t="n">
@@ -1406,12 +1406,12 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="15" t="n">
@@ -1478,27 +1478,27 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
@@ -1529,16 +1529,16 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2127.2</v>
+        <v>769.5</v>
       </c>
       <c r="O11" s="16" t="n">
         <v>0</v>
@@ -1550,32 +1550,32 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
@@ -1601,16 +1601,16 @@
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O12" s="16" t="n">
         <v>0</v>
@@ -1622,32 +1622,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
@@ -1673,16 +1673,16 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1694,12 +1694,12 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
@@ -1745,16 +1745,16 @@
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>0</v>
@@ -1766,27 +1766,27 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
@@ -1817,16 +1817,16 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O15" s="16" t="n">
         <v>0</v>
@@ -1838,12 +1838,12 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
@@ -1889,16 +1889,16 @@
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>0</v>
@@ -1910,12 +1910,12 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
@@ -1961,16 +1961,16 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1982,27 +1982,27 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
@@ -2033,16 +2033,16 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2054,32 +2054,32 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
@@ -2105,16 +2105,16 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2126,27 +2126,27 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2173,20 +2173,20 @@
         <v>3</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2198,12 +2198,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2238,29 +2238,29 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="O21" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="12" t="n">
@@ -2270,12 +2270,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2317,22 +2317,22 @@
         <v>3</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="15" t="n">
@@ -2342,27 +2342,27 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
@@ -2393,16 +2393,16 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2414,27 +2414,27 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2454,27 +2454,27 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>171.4</v>
+        <v>920</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2486,32 +2486,32 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
@@ -2537,16 +2537,16 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>0</v>
@@ -2558,27 +2558,27 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2609,16 +2609,16 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2630,27 +2630,27 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2681,16 +2681,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2702,32 +2702,32 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
@@ -2753,16 +2753,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2774,32 +2774,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2825,16 +2825,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2846,12 +2846,12 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2886,27 +2886,27 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2918,32 +2918,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2953,32 +2953,32 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2990,27 +2990,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="O32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="15" t="n">
@@ -3062,12 +3062,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3102,29 +3102,29 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="12" t="n">
@@ -3134,32 +3134,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3169,32 +3169,32 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3206,27 +3206,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3257,16 +3257,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3278,32 +3278,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
@@ -3329,16 +3329,16 @@
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3350,32 +3350,32 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3385,32 +3385,32 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3422,12 +3422,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
@@ -3473,16 +3473,16 @@
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>285</v>
+        <v>590.15</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3494,32 +3494,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3545,16 +3545,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3566,12 +3566,12 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3617,16 +3617,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3638,32 +3638,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -3689,16 +3689,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3710,27 +3710,27 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K42" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3782,12 +3782,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3833,16 +3833,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3854,32 +3854,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
@@ -3905,16 +3905,16 @@
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3926,32 +3926,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3977,16 +3977,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3998,12 +3998,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
@@ -4049,16 +4049,16 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4070,12 +4070,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4121,16 +4121,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4142,12 +4142,12 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4182,27 +4182,27 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K48" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4214,32 +4214,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4265,16 +4265,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4286,27 +4286,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4326,27 +4326,27 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4409,16 +4409,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4430,32 +4430,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4465,35 +4465,35 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K52" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="15" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O52" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
         <v>0</v>
@@ -4502,32 +4502,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O53" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O53" s="12" t="n">
+        <v>362.5</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
@@ -4574,12 +4574,12 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -4589,11 +4589,13 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
@@ -4612,27 +4614,27 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K54" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>1212</v>
+        <v>1320</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4644,67 +4646,53 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr"/>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27373</t>
-        </is>
-      </c>
-      <c r="M55" s="11" t="inlineStr">
-        <is>
-          <t>466234</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr"/>
       <c r="N55" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4714,22 +4702,22 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E56" s="14" t="n">
@@ -4747,32 +4735,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K56" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>230</v>
+        <v>1212</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4784,22 +4772,22 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -4807,7 +4795,7 @@
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4817,32 +4805,32 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>240</v>
+        <v>401</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4854,12 +4842,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -4869,7 +4857,7 @@
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E58" s="14" t="n">
@@ -4892,61 +4880,381 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
+          <t>14/04/2025</t>
+        </is>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="K58" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M58" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
+      <c r="N58" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H59" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N59" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
           <t>12/12/2024</t>
         </is>
       </c>
-      <c r="J58" s="14" t="n">
+      <c r="J60" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="K58" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="14" t="inlineStr">
+      <c r="K60" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-28023</t>
         </is>
       </c>
-      <c r="M58" s="14" t="inlineStr">
+      <c r="M60" s="14" t="inlineStr">
         <is>
           <t>454387</t>
         </is>
       </c>
-      <c r="N58" s="15" t="n">
+      <c r="N60" s="15" t="n">
         <v>557.145</v>
       </c>
-      <c r="O58" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="O60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-13128</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H61" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>30/10/2023</t>
+        </is>
+      </c>
+      <c r="J61" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K61" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L61" s="11" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr"/>
+      <c r="N61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12708</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr"/>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K62" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L62" s="14" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+      <c r="N62" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr"/>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr"/>
+      <c r="N63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr"/>
-      <c r="C59" s="17" t="inlineStr"/>
-      <c r="D59" s="17" t="inlineStr"/>
-      <c r="E59" s="17" t="inlineStr"/>
-      <c r="F59" s="17" t="inlineStr"/>
-      <c r="G59" s="17" t="inlineStr"/>
-      <c r="H59" s="17" t="inlineStr"/>
-      <c r="I59" s="17" t="inlineStr"/>
-      <c r="J59" s="17" t="inlineStr"/>
-      <c r="K59" s="17" t="inlineStr"/>
-      <c r="L59" s="17" t="inlineStr"/>
-      <c r="M59" s="17" t="inlineStr"/>
-      <c r="N59" s="18" t="n">
+      <c r="B64" s="17" t="inlineStr"/>
+      <c r="C64" s="17" t="inlineStr"/>
+      <c r="D64" s="17" t="inlineStr"/>
+      <c r="E64" s="17" t="inlineStr"/>
+      <c r="F64" s="17" t="inlineStr"/>
+      <c r="G64" s="17" t="inlineStr"/>
+      <c r="H64" s="17" t="inlineStr"/>
+      <c r="I64" s="17" t="inlineStr"/>
+      <c r="J64" s="17" t="inlineStr"/>
+      <c r="K64" s="17" t="inlineStr"/>
+      <c r="L64" s="17" t="inlineStr"/>
+      <c r="M64" s="17" t="inlineStr"/>
+      <c r="N64" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O59" s="18" t="n">
+      <c r="O64" s="18" t="n">
         <v>362.5</v>
       </c>
-      <c r="P59" s="18" t="n">
-        <v>76.31999999999999</v>
+      <c r="P64" s="18" t="n">
+        <v>25.89</v>
       </c>
     </row>
   </sheetData>
@@ -5006,6 +5314,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5580,26 +5893,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>0.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1.75</v>
+        <v>10</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5954,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>4.5</v>
+        <v>8.75</v>
       </c>
     </row>
   </sheetData>
@@ -5805,13 +6118,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -5829,7 +6142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 1 commande(s)</t>
+          <t>Épics créées ce mois — 2 commande(s)</t>
         </is>
       </c>
     </row>
@@ -5884,73 +6197,97 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-35410</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35401</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>00173074</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-35392</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-35385</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>00179700</t>
         </is>
       </c>
-      <c r="I5" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>1 commande(s)</t>
-        </is>
-      </c>
-      <c r="I6" s="24" t="n">
+      <c r="I6" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B7" s="17" t="n"/>
@@ -5961,7 +6298,7 @@
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>0 commande(s)</t>
+          <t>2 commande(s)</t>
         </is>
       </c>
       <c r="I7" s="24" t="n">
@@ -5971,7 +6308,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B8" s="17" t="n"/>
@@ -5982,10 +6319,31 @@
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>0 commande(s)</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>2 commande(s)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="n">
         <v>0</v>
       </c>
     </row>
